--- a/data/axe1/ALTERMAP_2026_Vision_du_Monde_SMA_labels_V3.xlsx
+++ b/data/axe1/ALTERMAP_2026_Vision_du_Monde_SMA_labels_V3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/claudegrasland1/worldregio/altermap/data/axe1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/claudegrasland1/Desktop/Altermap_axe1/data/axe1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B18ACFEB-6918-6347-AF42-2DDA3E96FC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79E87CCE-50E2-514E-8A62-D926B5294758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTERMAP 2026 - Vision du Monde" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8322" uniqueCount="2162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8651" uniqueCount="2229">
   <si>
     <t>start</t>
   </si>
@@ -6506,6 +6506,207 @@
   </si>
   <si>
     <t>uuid:b9dfdd16-526b-409a-9b2c-d203bb91e703</t>
+  </si>
+  <si>
+    <t>Dévekoppement</t>
+  </si>
+  <si>
+    <t>Fraternité</t>
+  </si>
+  <si>
+    <t>95-13_55_28.pdf</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aebDtX7eF2mAd7KqSMMtQi/data/747817103/attachments/attD3thSyWozTXkBsBCix4AS/</t>
+  </si>
+  <si>
+    <t>Atlantique Nord</t>
+  </si>
+  <si>
+    <t>b3fcd91a-2655-4992-8ed7-24e784031a88</t>
+  </si>
+  <si>
+    <t>uuid:b3fcd91a-2655-4992-8ed7-24e784031a88</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Egalité</t>
+  </si>
+  <si>
+    <t>Individualisme</t>
+  </si>
+  <si>
+    <t>Guerre civile</t>
+  </si>
+  <si>
+    <t>Drogue</t>
+  </si>
+  <si>
+    <t>Coup d'Etat</t>
+  </si>
+  <si>
+    <t>119-14_1_38.pdf</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aebDtX7eF2mAd7KqSMMtQi/data/747820434/attachments/att3yKEyhommNci9w3UUobNh/</t>
+  </si>
+  <si>
+    <t>cheikhoumaldiop9@gmail.com</t>
+  </si>
+  <si>
+    <t>733e8839-7886-4187-9589-a1c999ee4acc</t>
+  </si>
+  <si>
+    <t>uuid:733e8839-7886-4187-9589-a1c999ee4acc</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>Monument</t>
+  </si>
+  <si>
+    <t>Politique</t>
+  </si>
+  <si>
+    <t>Normes</t>
+  </si>
+  <si>
+    <t>Respect des droits</t>
+  </si>
+  <si>
+    <t>Malheur</t>
+  </si>
+  <si>
+    <t>Peur</t>
+  </si>
+  <si>
+    <t>Obstacle</t>
+  </si>
+  <si>
+    <t>134-14_8_13.pdf</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aebDtX7eF2mAd7KqSMMtQi/data/747824187/attachments/attPKpKbdtb9zfTtHhL3kJ8v/</t>
+  </si>
+  <si>
+    <t>Centre-Afrique</t>
+  </si>
+  <si>
+    <t>Etats Unis</t>
+  </si>
+  <si>
+    <t>lysadiop069@gmail.com</t>
+  </si>
+  <si>
+    <t>c20b4205-6b33-459f-b5d9-3a3a77230003</t>
+  </si>
+  <si>
+    <t>uuid:c20b4205-6b33-459f-b5d9-3a3a77230003</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Recherche sientifique</t>
+  </si>
+  <si>
+    <t>Développement technologique</t>
+  </si>
+  <si>
+    <t>Programmes</t>
+  </si>
+  <si>
+    <t>Carrefour des continents</t>
+  </si>
+  <si>
+    <t>Migrations</t>
+  </si>
+  <si>
+    <t>Tourisme et littoraux</t>
+  </si>
+  <si>
+    <t>Civilisation antique</t>
+  </si>
+  <si>
+    <t>Jeunesse de la population</t>
+  </si>
+  <si>
+    <t>Enjeux climatique</t>
+  </si>
+  <si>
+    <t>Dynamique de développement</t>
+  </si>
+  <si>
+    <t>133-14_17_7.pdf</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aebDtX7eF2mAd7KqSMMtQi/data/747828905/attachments/attnrnbvSdbeDwqNjvqYCm6T/</t>
+  </si>
+  <si>
+    <t>Corée du nord</t>
+  </si>
+  <si>
+    <t>e88f7eeb-3aa6-4d93-8e27-96756db8cc96</t>
+  </si>
+  <si>
+    <t>uuid:e88f7eeb-3aa6-4d93-8e27-96756db8cc96</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Le continent pauvre historique</t>
+  </si>
+  <si>
+    <t>Le plus riche en biens</t>
+  </si>
+  <si>
+    <t>Lieu de rêve du monde</t>
+  </si>
+  <si>
+    <t>Continent des espions</t>
+  </si>
+  <si>
+    <t>Peuple stratégique</t>
+  </si>
+  <si>
+    <t>Zone bleu du monde</t>
+  </si>
+  <si>
+    <t>Entourage de la terre</t>
+  </si>
+  <si>
+    <t>Zone d'épanouissement</t>
+  </si>
+  <si>
+    <t>Surface halieutique</t>
+  </si>
+  <si>
+    <t>Richesse énergétique, minier</t>
+  </si>
+  <si>
+    <t>Base de richesse de l'Amérique</t>
+  </si>
+  <si>
+    <t>Continent historique du monde</t>
+  </si>
+  <si>
+    <t>Pilier important des guerres mondiales</t>
+  </si>
+  <si>
+    <t>64-14_36_37.pdf</t>
+  </si>
+  <si>
+    <t>https://kf.kobotoolbox.org/api/v2/assets/aebDtX7eF2mAd7KqSMMtQi/data/750096651/attachments/attLbXhQSkqBGHdR6SHdduPZ/</t>
+  </si>
+  <si>
+    <t>2b26025d-fb92-4013-8421-9af250ba1ec2</t>
+  </si>
+  <si>
+    <t>uuid:2b26025d-fb92-4013-8421-9af250ba1ec2</t>
   </si>
 </sst>
 </file>
@@ -6864,7 +7065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DZ144"/>
+  <dimension ref="A1:DZ149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:130" x14ac:dyDescent="0.2">
@@ -38887,6 +39088,1243 @@
       </c>
       <c r="DZ144">
         <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:130" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46150.583705914352</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46152.58131765046</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F145" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G145" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I145" t="s">
+        <v>125</v>
+      </c>
+      <c r="J145" t="s">
+        <v>126</v>
+      </c>
+      <c r="K145" t="s">
+        <v>127</v>
+      </c>
+      <c r="M145" t="s">
+        <v>128</v>
+      </c>
+      <c r="N145">
+        <v>2002</v>
+      </c>
+      <c r="O145" t="s">
+        <v>156</v>
+      </c>
+      <c r="P145" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>156</v>
+      </c>
+      <c r="R145" t="s">
+        <v>156</v>
+      </c>
+      <c r="T145" t="s">
+        <v>970</v>
+      </c>
+      <c r="X145" t="s">
+        <v>970</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB145" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK145">
+        <v>6</v>
+      </c>
+      <c r="AL145">
+        <v>8</v>
+      </c>
+      <c r="AM145">
+        <v>8</v>
+      </c>
+      <c r="AO145" t="s">
+        <v>814</v>
+      </c>
+      <c r="AP145">
+        <v>0</v>
+      </c>
+      <c r="AQ145">
+        <v>1</v>
+      </c>
+      <c r="AR145">
+        <v>1</v>
+      </c>
+      <c r="AS145">
+        <v>1</v>
+      </c>
+      <c r="AT145">
+        <v>0</v>
+      </c>
+      <c r="AU145">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="s">
+        <v>137</v>
+      </c>
+      <c r="AX145" t="s">
+        <v>183</v>
+      </c>
+      <c r="AY145" t="s">
+        <v>129</v>
+      </c>
+      <c r="AZ145" t="s">
+        <v>159</v>
+      </c>
+      <c r="BA145" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB145" t="s">
+        <v>138</v>
+      </c>
+      <c r="BC145" t="s">
+        <v>566</v>
+      </c>
+      <c r="BD145" t="s">
+        <v>481</v>
+      </c>
+      <c r="BE145" t="s">
+        <v>144</v>
+      </c>
+      <c r="BF145" t="s">
+        <v>1074</v>
+      </c>
+      <c r="BG145" t="s">
+        <v>382</v>
+      </c>
+      <c r="BH145" t="s">
+        <v>2162</v>
+      </c>
+      <c r="BI145" t="s">
+        <v>254</v>
+      </c>
+      <c r="BJ145" t="s">
+        <v>265</v>
+      </c>
+      <c r="BK145" t="s">
+        <v>1313</v>
+      </c>
+      <c r="BM145" t="s">
+        <v>1110</v>
+      </c>
+      <c r="BN145" t="s">
+        <v>1077</v>
+      </c>
+      <c r="BO145" t="s">
+        <v>280</v>
+      </c>
+      <c r="BP145" t="s">
+        <v>194</v>
+      </c>
+      <c r="BQ145" t="s">
+        <v>1079</v>
+      </c>
+      <c r="BR145" t="s">
+        <v>265</v>
+      </c>
+      <c r="BS145" t="s">
+        <v>2163</v>
+      </c>
+      <c r="BT145" t="s">
+        <v>1431</v>
+      </c>
+      <c r="BU145" t="s">
+        <v>262</v>
+      </c>
+      <c r="BY145" t="s">
+        <v>2164</v>
+      </c>
+      <c r="BZ145" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="CA145" t="s">
+        <v>165</v>
+      </c>
+      <c r="CC145" t="s">
+        <v>163</v>
+      </c>
+      <c r="CE145" t="s">
+        <v>161</v>
+      </c>
+      <c r="CG145" t="s">
+        <v>160</v>
+      </c>
+      <c r="CI145" t="s">
+        <v>238</v>
+      </c>
+      <c r="CK145" t="s">
+        <v>221</v>
+      </c>
+      <c r="CM145" t="s">
+        <v>240</v>
+      </c>
+      <c r="CO145" t="s">
+        <v>164</v>
+      </c>
+      <c r="CQ145" t="s">
+        <v>199</v>
+      </c>
+      <c r="CS145" t="s">
+        <v>337</v>
+      </c>
+      <c r="CU145" t="s">
+        <v>166</v>
+      </c>
+      <c r="CV145" t="s">
+        <v>2166</v>
+      </c>
+      <c r="CW145" t="s">
+        <v>166</v>
+      </c>
+      <c r="CX145" t="s">
+        <v>1178</v>
+      </c>
+      <c r="DM145" t="s">
+        <v>202</v>
+      </c>
+      <c r="DP145">
+        <v>747817103</v>
+      </c>
+      <c r="DQ145" t="s">
+        <v>2167</v>
+      </c>
+      <c r="DR145" s="1">
+        <v>46152.581354166658</v>
+      </c>
+      <c r="DU145" t="s">
+        <v>174</v>
+      </c>
+      <c r="DW145" t="s">
+        <v>1086</v>
+      </c>
+      <c r="DY145" t="s">
+        <v>2168</v>
+      </c>
+      <c r="DZ145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:130" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46152.581318391203</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46152.586384745373</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E146" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F146" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G146" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I146" t="s">
+        <v>125</v>
+      </c>
+      <c r="J146" t="s">
+        <v>126</v>
+      </c>
+      <c r="K146" t="s">
+        <v>127</v>
+      </c>
+      <c r="M146" t="s">
+        <v>272</v>
+      </c>
+      <c r="N146">
+        <v>2001</v>
+      </c>
+      <c r="O146" t="s">
+        <v>156</v>
+      </c>
+      <c r="P146" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>156</v>
+      </c>
+      <c r="R146" t="s">
+        <v>156</v>
+      </c>
+      <c r="T146" t="s">
+        <v>970</v>
+      </c>
+      <c r="X146" t="s">
+        <v>970</v>
+      </c>
+      <c r="Y146" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB146" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK146">
+        <v>0</v>
+      </c>
+      <c r="AL146">
+        <v>0</v>
+      </c>
+      <c r="AM146">
+        <v>0</v>
+      </c>
+      <c r="AO146" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP146">
+        <v>1</v>
+      </c>
+      <c r="AQ146">
+        <v>1</v>
+      </c>
+      <c r="AR146">
+        <v>1</v>
+      </c>
+      <c r="AS146">
+        <v>0</v>
+      </c>
+      <c r="AT146">
+        <v>0</v>
+      </c>
+      <c r="AU146">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="s">
+        <v>274</v>
+      </c>
+      <c r="AX146" t="s">
+        <v>183</v>
+      </c>
+      <c r="AY146" t="s">
+        <v>231</v>
+      </c>
+      <c r="AZ146" t="s">
+        <v>129</v>
+      </c>
+      <c r="BA146" t="s">
+        <v>143</v>
+      </c>
+      <c r="BB146" t="s">
+        <v>275</v>
+      </c>
+      <c r="BC146" t="s">
+        <v>685</v>
+      </c>
+      <c r="BD146" t="s">
+        <v>156</v>
+      </c>
+      <c r="BE146" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF146" t="s">
+        <v>1272</v>
+      </c>
+      <c r="BG146" t="s">
+        <v>481</v>
+      </c>
+      <c r="BH146" t="s">
+        <v>1257</v>
+      </c>
+      <c r="BI146" t="s">
+        <v>254</v>
+      </c>
+      <c r="BJ146" t="s">
+        <v>1577</v>
+      </c>
+      <c r="BK146" t="s">
+        <v>2170</v>
+      </c>
+      <c r="BL146" t="s">
+        <v>2171</v>
+      </c>
+      <c r="BM146" t="s">
+        <v>262</v>
+      </c>
+      <c r="BN146" t="s">
+        <v>2172</v>
+      </c>
+      <c r="BO146" t="s">
+        <v>1218</v>
+      </c>
+      <c r="BP146" t="s">
+        <v>1277</v>
+      </c>
+      <c r="BQ146" t="s">
+        <v>2173</v>
+      </c>
+      <c r="BR146" t="s">
+        <v>2174</v>
+      </c>
+      <c r="BS146" t="s">
+        <v>1218</v>
+      </c>
+      <c r="BT146" t="s">
+        <v>1233</v>
+      </c>
+      <c r="BU146" t="s">
+        <v>262</v>
+      </c>
+      <c r="BV146" t="s">
+        <v>2172</v>
+      </c>
+      <c r="BY146" t="s">
+        <v>2175</v>
+      </c>
+      <c r="BZ146" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="CA146" t="s">
+        <v>165</v>
+      </c>
+      <c r="CC146" t="s">
+        <v>164</v>
+      </c>
+      <c r="CE146" t="s">
+        <v>199</v>
+      </c>
+      <c r="CG146" t="s">
+        <v>240</v>
+      </c>
+      <c r="CI146" t="s">
+        <v>221</v>
+      </c>
+      <c r="CK146" t="s">
+        <v>329</v>
+      </c>
+      <c r="CM146" t="s">
+        <v>619</v>
+      </c>
+      <c r="CO146" t="s">
+        <v>606</v>
+      </c>
+      <c r="CQ146" t="s">
+        <v>630</v>
+      </c>
+      <c r="CS146" t="s">
+        <v>219</v>
+      </c>
+      <c r="CU146" t="s">
+        <v>166</v>
+      </c>
+      <c r="CV146" t="s">
+        <v>1913</v>
+      </c>
+      <c r="CW146" t="s">
+        <v>163</v>
+      </c>
+      <c r="CY146" t="s">
+        <v>166</v>
+      </c>
+      <c r="CZ146" t="s">
+        <v>1914</v>
+      </c>
+      <c r="DA146" t="s">
+        <v>171</v>
+      </c>
+      <c r="DC146" t="s">
+        <v>238</v>
+      </c>
+      <c r="DM146" t="s">
+        <v>131</v>
+      </c>
+      <c r="DN146" t="s">
+        <v>2177</v>
+      </c>
+      <c r="DP146">
+        <v>747820434</v>
+      </c>
+      <c r="DQ146" t="s">
+        <v>2178</v>
+      </c>
+      <c r="DR146" s="1">
+        <v>46152.586458333331</v>
+      </c>
+      <c r="DU146" t="s">
+        <v>174</v>
+      </c>
+      <c r="DW146" t="s">
+        <v>1086</v>
+      </c>
+      <c r="DY146" t="s">
+        <v>2179</v>
+      </c>
+      <c r="DZ146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:130" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46152.58638533565</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46152.59125326389</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E147" t="s">
+        <v>2180</v>
+      </c>
+      <c r="F147" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G147" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I147" t="s">
+        <v>125</v>
+      </c>
+      <c r="J147" t="s">
+        <v>126</v>
+      </c>
+      <c r="K147" t="s">
+        <v>127</v>
+      </c>
+      <c r="M147" t="s">
+        <v>128</v>
+      </c>
+      <c r="N147">
+        <v>1999</v>
+      </c>
+      <c r="O147" t="s">
+        <v>156</v>
+      </c>
+      <c r="P147" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>156</v>
+      </c>
+      <c r="R147" t="s">
+        <v>156</v>
+      </c>
+      <c r="T147" t="s">
+        <v>970</v>
+      </c>
+      <c r="X147" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>970</v>
+      </c>
+      <c r="AB147" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK147">
+        <v>0</v>
+      </c>
+      <c r="AL147">
+        <v>3</v>
+      </c>
+      <c r="AM147">
+        <v>0</v>
+      </c>
+      <c r="AO147" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP147">
+        <v>1</v>
+      </c>
+      <c r="AQ147">
+        <v>1</v>
+      </c>
+      <c r="AR147">
+        <v>1</v>
+      </c>
+      <c r="AS147">
+        <v>0</v>
+      </c>
+      <c r="AT147">
+        <v>0</v>
+      </c>
+      <c r="AU147">
+        <v>0</v>
+      </c>
+      <c r="AW147" t="s">
+        <v>274</v>
+      </c>
+      <c r="AX147" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY147" t="s">
+        <v>441</v>
+      </c>
+      <c r="AZ147" t="s">
+        <v>143</v>
+      </c>
+      <c r="BA147" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB147" t="s">
+        <v>134</v>
+      </c>
+      <c r="BC147" t="s">
+        <v>207</v>
+      </c>
+      <c r="BD147" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE147" t="s">
+        <v>182</v>
+      </c>
+      <c r="BF147" t="s">
+        <v>232</v>
+      </c>
+      <c r="BG147" t="s">
+        <v>139</v>
+      </c>
+      <c r="BH147" t="s">
+        <v>2181</v>
+      </c>
+      <c r="BI147" t="s">
+        <v>2182</v>
+      </c>
+      <c r="BJ147" t="s">
+        <v>2183</v>
+      </c>
+      <c r="BK147" t="s">
+        <v>2184</v>
+      </c>
+      <c r="BL147" t="s">
+        <v>1227</v>
+      </c>
+      <c r="BM147" t="s">
+        <v>2185</v>
+      </c>
+      <c r="BN147" t="s">
+        <v>1098</v>
+      </c>
+      <c r="BO147" t="s">
+        <v>2186</v>
+      </c>
+      <c r="BP147" t="s">
+        <v>233</v>
+      </c>
+      <c r="BQ147" t="s">
+        <v>2187</v>
+      </c>
+      <c r="BR147" t="s">
+        <v>234</v>
+      </c>
+      <c r="BS147" t="s">
+        <v>1116</v>
+      </c>
+      <c r="BT147" t="s">
+        <v>1924</v>
+      </c>
+      <c r="BU147" t="s">
+        <v>1921</v>
+      </c>
+      <c r="BV147" t="s">
+        <v>1146</v>
+      </c>
+      <c r="BY147" t="s">
+        <v>2188</v>
+      </c>
+      <c r="BZ147" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="CA147" t="s">
+        <v>165</v>
+      </c>
+      <c r="CC147" t="s">
+        <v>199</v>
+      </c>
+      <c r="CE147" t="s">
+        <v>166</v>
+      </c>
+      <c r="CF147" t="s">
+        <v>2190</v>
+      </c>
+      <c r="CG147" t="s">
+        <v>240</v>
+      </c>
+      <c r="CI147" t="s">
+        <v>164</v>
+      </c>
+      <c r="CK147" t="s">
+        <v>166</v>
+      </c>
+      <c r="CL147" t="s">
+        <v>441</v>
+      </c>
+      <c r="CM147" t="s">
+        <v>166</v>
+      </c>
+      <c r="CN147" t="s">
+        <v>232</v>
+      </c>
+      <c r="CO147" t="s">
+        <v>166</v>
+      </c>
+      <c r="CP147" t="s">
+        <v>1178</v>
+      </c>
+      <c r="CQ147" t="s">
+        <v>187</v>
+      </c>
+      <c r="CS147" t="s">
+        <v>207</v>
+      </c>
+      <c r="CU147" t="s">
+        <v>166</v>
+      </c>
+      <c r="CV147" t="s">
+        <v>211</v>
+      </c>
+      <c r="CW147" t="s">
+        <v>166</v>
+      </c>
+      <c r="CX147" t="s">
+        <v>2191</v>
+      </c>
+      <c r="CY147" t="s">
+        <v>166</v>
+      </c>
+      <c r="CZ147" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA147" t="s">
+        <v>166</v>
+      </c>
+      <c r="DB147" t="s">
+        <v>129</v>
+      </c>
+      <c r="DC147" t="s">
+        <v>166</v>
+      </c>
+      <c r="DD147" t="s">
+        <v>139</v>
+      </c>
+      <c r="DM147" t="s">
+        <v>131</v>
+      </c>
+      <c r="DN147" t="s">
+        <v>2192</v>
+      </c>
+      <c r="DP147">
+        <v>747824187</v>
+      </c>
+      <c r="DQ147" t="s">
+        <v>2193</v>
+      </c>
+      <c r="DR147" s="1">
+        <v>46152.591284722221</v>
+      </c>
+      <c r="DU147" t="s">
+        <v>174</v>
+      </c>
+      <c r="DW147" t="s">
+        <v>1086</v>
+      </c>
+      <c r="DY147" t="s">
+        <v>2194</v>
+      </c>
+      <c r="DZ147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:130" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46152.591254016203</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46152.596812569442</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E148" t="s">
+        <v>2195</v>
+      </c>
+      <c r="F148" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I148" t="s">
+        <v>125</v>
+      </c>
+      <c r="J148" t="s">
+        <v>126</v>
+      </c>
+      <c r="K148" t="s">
+        <v>127</v>
+      </c>
+      <c r="M148" t="s">
+        <v>128</v>
+      </c>
+      <c r="N148">
+        <v>1997</v>
+      </c>
+      <c r="O148" t="s">
+        <v>156</v>
+      </c>
+      <c r="P148" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>156</v>
+      </c>
+      <c r="R148" t="s">
+        <v>156</v>
+      </c>
+      <c r="T148" t="s">
+        <v>1438</v>
+      </c>
+      <c r="X148" t="s">
+        <v>1438</v>
+      </c>
+      <c r="Y148" t="s">
+        <v>970</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB148" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK148">
+        <v>3</v>
+      </c>
+      <c r="AL148">
+        <v>0</v>
+      </c>
+      <c r="AM148">
+        <v>8</v>
+      </c>
+      <c r="AO148" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP148">
+        <v>1</v>
+      </c>
+      <c r="AQ148">
+        <v>1</v>
+      </c>
+      <c r="AR148">
+        <v>1</v>
+      </c>
+      <c r="AS148">
+        <v>0</v>
+      </c>
+      <c r="AT148">
+        <v>0</v>
+      </c>
+      <c r="AU148">
+        <v>0</v>
+      </c>
+      <c r="AW148" t="s">
+        <v>274</v>
+      </c>
+      <c r="AX148" t="s">
+        <v>183</v>
+      </c>
+      <c r="AY148" t="s">
+        <v>182</v>
+      </c>
+      <c r="AZ148" t="s">
+        <v>129</v>
+      </c>
+      <c r="BA148" t="s">
+        <v>2037</v>
+      </c>
+      <c r="BB148" t="s">
+        <v>138</v>
+      </c>
+      <c r="BC148" t="s">
+        <v>185</v>
+      </c>
+      <c r="BD148" t="s">
+        <v>358</v>
+      </c>
+      <c r="BE148" t="s">
+        <v>465</v>
+      </c>
+      <c r="BF148" t="s">
+        <v>567</v>
+      </c>
+      <c r="BG148" t="s">
+        <v>610</v>
+      </c>
+      <c r="BH148" t="s">
+        <v>2196</v>
+      </c>
+      <c r="BI148" t="s">
+        <v>188</v>
+      </c>
+      <c r="BJ148" t="s">
+        <v>1611</v>
+      </c>
+      <c r="BK148" t="s">
+        <v>2197</v>
+      </c>
+      <c r="BL148" t="s">
+        <v>2198</v>
+      </c>
+      <c r="BM148" t="s">
+        <v>2199</v>
+      </c>
+      <c r="BN148" t="s">
+        <v>1315</v>
+      </c>
+      <c r="BO148" t="s">
+        <v>2200</v>
+      </c>
+      <c r="BP148" t="s">
+        <v>2201</v>
+      </c>
+      <c r="BQ148" t="s">
+        <v>2202</v>
+      </c>
+      <c r="BR148" t="s">
+        <v>1188</v>
+      </c>
+      <c r="BS148" t="s">
+        <v>2203</v>
+      </c>
+      <c r="BT148" t="s">
+        <v>2204</v>
+      </c>
+      <c r="BU148" t="s">
+        <v>1247</v>
+      </c>
+      <c r="BV148" t="s">
+        <v>2205</v>
+      </c>
+      <c r="BY148" t="s">
+        <v>2206</v>
+      </c>
+      <c r="BZ148" s="2" t="s">
+        <v>2207</v>
+      </c>
+      <c r="CA148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CB148" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CD148" t="s">
+        <v>182</v>
+      </c>
+      <c r="CE148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CF148" t="s">
+        <v>129</v>
+      </c>
+      <c r="CG148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CH148" t="s">
+        <v>2037</v>
+      </c>
+      <c r="CI148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CJ148" t="s">
+        <v>138</v>
+      </c>
+      <c r="CK148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CL148" t="s">
+        <v>185</v>
+      </c>
+      <c r="CM148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CN148" t="s">
+        <v>2208</v>
+      </c>
+      <c r="CO148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CP148" t="s">
+        <v>465</v>
+      </c>
+      <c r="CQ148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CR148" t="s">
+        <v>567</v>
+      </c>
+      <c r="CS148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CT148" t="s">
+        <v>610</v>
+      </c>
+      <c r="CU148" t="s">
+        <v>166</v>
+      </c>
+      <c r="CV148" t="s">
+        <v>267</v>
+      </c>
+      <c r="DM148" t="s">
+        <v>202</v>
+      </c>
+      <c r="DP148">
+        <v>747828905</v>
+      </c>
+      <c r="DQ148" t="s">
+        <v>2209</v>
+      </c>
+      <c r="DR148" s="1">
+        <v>46152.59684027778</v>
+      </c>
+      <c r="DU148" t="s">
+        <v>174</v>
+      </c>
+      <c r="DW148" t="s">
+        <v>1086</v>
+      </c>
+      <c r="DY148" t="s">
+        <v>2210</v>
+      </c>
+      <c r="DZ148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:130" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>46152.596813206022</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46154.60912710648</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E149" t="s">
+        <v>2211</v>
+      </c>
+      <c r="F149" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I149" t="s">
+        <v>125</v>
+      </c>
+      <c r="J149" t="s">
+        <v>126</v>
+      </c>
+      <c r="K149" t="s">
+        <v>127</v>
+      </c>
+      <c r="M149" t="s">
+        <v>272</v>
+      </c>
+      <c r="N149">
+        <v>1998</v>
+      </c>
+      <c r="O149" t="s">
+        <v>156</v>
+      </c>
+      <c r="P149" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>156</v>
+      </c>
+      <c r="R149" t="s">
+        <v>156</v>
+      </c>
+      <c r="T149" t="s">
+        <v>1312</v>
+      </c>
+      <c r="X149" t="s">
+        <v>1312</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>970</v>
+      </c>
+      <c r="AB149" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK149">
+        <v>0</v>
+      </c>
+      <c r="AL149">
+        <v>3</v>
+      </c>
+      <c r="AM149">
+        <v>8</v>
+      </c>
+      <c r="AO149" t="s">
+        <v>335</v>
+      </c>
+      <c r="AP149">
+        <v>1</v>
+      </c>
+      <c r="AQ149">
+        <v>1</v>
+      </c>
+      <c r="AR149">
+        <v>1</v>
+      </c>
+      <c r="AS149">
+        <v>1</v>
+      </c>
+      <c r="AT149">
+        <v>1</v>
+      </c>
+      <c r="AU149">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="s">
+        <v>274</v>
+      </c>
+      <c r="AX149" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY149" t="s">
+        <v>183</v>
+      </c>
+      <c r="AZ149" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA149" t="s">
+        <v>143</v>
+      </c>
+      <c r="BB149" t="s">
+        <v>207</v>
+      </c>
+      <c r="BC149" t="s">
+        <v>357</v>
+      </c>
+      <c r="BD149" t="s">
+        <v>441</v>
+      </c>
+      <c r="BE149" t="s">
+        <v>248</v>
+      </c>
+      <c r="BF149" t="s">
+        <v>382</v>
+      </c>
+      <c r="BG149" t="s">
+        <v>186</v>
+      </c>
+      <c r="BH149" t="s">
+        <v>2212</v>
+      </c>
+      <c r="BI149" t="s">
+        <v>2213</v>
+      </c>
+      <c r="BJ149" t="s">
+        <v>2214</v>
+      </c>
+      <c r="BK149" t="s">
+        <v>2215</v>
+      </c>
+      <c r="BL149" t="s">
+        <v>2216</v>
+      </c>
+      <c r="BM149" t="s">
+        <v>2217</v>
+      </c>
+      <c r="BN149" t="s">
+        <v>2218</v>
+      </c>
+      <c r="BO149" t="s">
+        <v>1509</v>
+      </c>
+      <c r="BP149" t="s">
+        <v>2219</v>
+      </c>
+      <c r="BQ149" t="s">
+        <v>2220</v>
+      </c>
+      <c r="BR149" t="s">
+        <v>2221</v>
+      </c>
+      <c r="BS149" t="s">
+        <v>1568</v>
+      </c>
+      <c r="BT149" t="s">
+        <v>2222</v>
+      </c>
+      <c r="BU149" t="s">
+        <v>2223</v>
+      </c>
+      <c r="BV149" t="s">
+        <v>2224</v>
+      </c>
+      <c r="BY149" t="s">
+        <v>2225</v>
+      </c>
+      <c r="BZ149" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="CA149" t="s">
+        <v>267</v>
+      </c>
+      <c r="CC149" t="s">
+        <v>762</v>
+      </c>
+      <c r="CE149" t="s">
+        <v>160</v>
+      </c>
+      <c r="CG149" t="s">
+        <v>171</v>
+      </c>
+      <c r="CI149" t="s">
+        <v>238</v>
+      </c>
+      <c r="DM149" t="s">
+        <v>202</v>
+      </c>
+      <c r="DP149">
+        <v>750096651</v>
+      </c>
+      <c r="DQ149" t="s">
+        <v>2227</v>
+      </c>
+      <c r="DR149" s="1">
+        <v>46154.609305555547</v>
+      </c>
+      <c r="DU149" t="s">
+        <v>174</v>
+      </c>
+      <c r="DW149" t="s">
+        <v>1086</v>
+      </c>
+      <c r="DY149" t="s">
+        <v>2228</v>
+      </c>
+      <c r="DZ149">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -38976,6 +40414,11 @@
     <hyperlink ref="BZ142" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
     <hyperlink ref="BZ143" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
     <hyperlink ref="BZ144" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="BZ145" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="BZ146" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="BZ147" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="BZ148" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="BZ149" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
